--- a/data/Mörel-Filet/investment_decision/Filet_MFH_until_2004_investment_decision.xlsx
+++ b/data/Mörel-Filet/investment_decision/Filet_MFH_until_2004_investment_decision.xlsx
@@ -495,7 +495,7 @@
         <v>46023</v>
       </c>
       <c r="B2" t="n">
-        <v>3.373073821365985</v>
+        <v>4.080605491068899</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -509,19 +509,19 @@
         <v>1179.679686608365</v>
       </c>
       <c r="F2" t="n">
-        <v>3.379384213644426</v>
+        <v>4.0806054910689</v>
       </c>
       <c r="G2" t="n">
         <v>1179.679686608365</v>
       </c>
       <c r="H2" t="n">
-        <v>3.381074201513377</v>
+        <v>4.080605491068903</v>
       </c>
       <c r="I2" t="n">
         <v>1179.679686608365</v>
       </c>
       <c r="J2" t="n">
-        <v>3.374559042927014</v>
+        <v>4.026994042360394</v>
       </c>
       <c r="K2" t="n">
         <v>1179.679686608365</v>
@@ -532,7 +532,7 @@
         <v>47849</v>
       </c>
       <c r="B3" t="n">
-        <v>3.373073821365985</v>
+        <v>4.080605491068899</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -546,19 +546,19 @@
         <v>1179.679686608365</v>
       </c>
       <c r="F3" t="n">
-        <v>3.379384213644426</v>
+        <v>4.0806054910689</v>
       </c>
       <c r="G3" t="n">
         <v>1179.679686608365</v>
       </c>
       <c r="H3" t="n">
-        <v>3.381074201513377</v>
+        <v>4.080605491068903</v>
       </c>
       <c r="I3" t="n">
         <v>1179.679686608365</v>
       </c>
       <c r="J3" t="n">
-        <v>3.374559042927014</v>
+        <v>4.026994042360394</v>
       </c>
       <c r="K3" t="n">
         <v>1179.679686608365</v>
@@ -569,7 +569,7 @@
         <v>49675</v>
       </c>
       <c r="B4" t="n">
-        <v>3.373073821365985</v>
+        <v>4.080605491068899</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -583,19 +583,19 @@
         <v>1179.679686608365</v>
       </c>
       <c r="F4" t="n">
-        <v>3.379384213644426</v>
+        <v>4.0806054910689</v>
       </c>
       <c r="G4" t="n">
         <v>1179.679686608365</v>
       </c>
       <c r="H4" t="n">
-        <v>3.381074201513377</v>
+        <v>4.080605491068903</v>
       </c>
       <c r="I4" t="n">
         <v>1179.679686608365</v>
       </c>
       <c r="J4" t="n">
-        <v>3.374559042927014</v>
+        <v>4.026994042360394</v>
       </c>
       <c r="K4" t="n">
         <v>1179.679686608365</v>
@@ -606,7 +606,7 @@
         <v>51502</v>
       </c>
       <c r="B5" t="n">
-        <v>3.376272389177037</v>
+        <v>4.080605491068899</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -620,19 +620,19 @@
         <v>1179.679686608365</v>
       </c>
       <c r="F5" t="n">
-        <v>3.379442064886244</v>
+        <v>4.0806054910689</v>
       </c>
       <c r="G5" t="n">
         <v>1179.679686608365</v>
       </c>
       <c r="H5" t="n">
-        <v>3.381074201513376</v>
+        <v>4.080605491068903</v>
       </c>
       <c r="I5" t="n">
         <v>1179.679686608365</v>
       </c>
       <c r="J5" t="n">
-        <v>3.376272389177037</v>
+        <v>4.026994042360394</v>
       </c>
       <c r="K5" t="n">
         <v>1179.679686608365</v>
@@ -643,7 +643,7 @@
         <v>53328</v>
       </c>
       <c r="B6" t="n">
-        <v>3.376272389177037</v>
+        <v>4.080605491068899</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -657,19 +657,19 @@
         <v>1179.679686608365</v>
       </c>
       <c r="F6" t="n">
-        <v>3.379442064886244</v>
+        <v>4.0806054910689</v>
       </c>
       <c r="G6" t="n">
         <v>1179.679686608365</v>
       </c>
       <c r="H6" t="n">
-        <v>3.381074201513376</v>
+        <v>4.080605491068903</v>
       </c>
       <c r="I6" t="n">
         <v>1179.679686608365</v>
       </c>
       <c r="J6" t="n">
-        <v>3.376272389177037</v>
+        <v>4.026994042360394</v>
       </c>
       <c r="K6" t="n">
         <v>1179.679686608365</v>
@@ -684,32 +684,32 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Filet_b_MFH_until_2004</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Filet_b_MFH_until_2004</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E7" t="n">
-        <v>1.769519529912548</v>
+        <v>1.755</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>1.769519529912548</v>
+        <v>1.755</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>1.016118366287013</v>
+        <v>1.00778075782065</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>1.016118366287013</v>
+        <v>1.00778075782065</v>
       </c>
     </row>
     <row r="8">
@@ -721,32 +721,32 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Filet_b_MFH_until_2004</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Filet_b_MFH_until_2004</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E8" t="n">
-        <v>1.769519529912548</v>
+        <v>1.755</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>1.769519529912548</v>
+        <v>1.755</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>1.314036394264725</v>
+        <v>1.303254263629724</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>1.314036394264725</v>
+        <v>1.303254263629724</v>
       </c>
     </row>
     <row r="9">
@@ -758,32 +758,32 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Filet_b_MFH_until_2004</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Filet_b_MFH_until_2004</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E9" t="n">
-        <v>1.769519529912548</v>
+        <v>1.755</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>1.769519529912548</v>
+        <v>1.755</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>1.446712058416415</v>
+        <v>1.434841277307795</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>1.446712058416415</v>
+        <v>1.434841277307795</v>
       </c>
     </row>
     <row r="10">
@@ -795,32 +795,32 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Filet_b_MFH_until_2004</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Filet_b_MFH_until_2004</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E10" t="n">
-        <v>1.769519529912548</v>
+        <v>1.755</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>1.769519529912548</v>
+        <v>1.755</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>1.519414860355694</v>
+        <v>1.506947527194587</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>1.519414860355694</v>
+        <v>1.506947527194587</v>
       </c>
     </row>
     <row r="11">
@@ -832,32 +832,32 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Filet_b_MFH_until_2004</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Filet_b_MFH_until_2004</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E11" t="n">
-        <v>1.769519529912548</v>
+        <v>1.755</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>1.769519529912548</v>
+        <v>1.755</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>1.564554801150552</v>
+        <v>1.551717078903854</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>1.564554801150552</v>
+        <v>1.551717078903854</v>
       </c>
     </row>
     <row r="12">
@@ -865,7 +865,7 @@
         <v>46023</v>
       </c>
       <c r="B12" t="n">
-        <v>0.0003431676904081859</v>
+        <v>0.0002802934588235294</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -879,19 +879,19 @@
         <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0003435431977095578</v>
+        <v>0.0002802934588235294</v>
       </c>
       <c r="G12" t="n">
         <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>0.0003436062498899332</v>
+        <v>0.0002802934588235294</v>
       </c>
       <c r="I12" t="n">
         <v>1</v>
       </c>
       <c r="J12" t="n">
-        <v>0.0003430974112518748</v>
+        <v>0.0002802934588235294</v>
       </c>
       <c r="K12" t="n">
         <v>1</v>
@@ -902,7 +902,7 @@
         <v>47849</v>
       </c>
       <c r="B13" t="n">
-        <v>0.0003431676904081859</v>
+        <v>0.0002802934588235295</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -916,19 +916,19 @@
         <v>1</v>
       </c>
       <c r="F13" t="n">
-        <v>0.0003435431977095578</v>
+        <v>0.0002802934588235295</v>
       </c>
       <c r="G13" t="n">
         <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>0.0003436062498899332</v>
+        <v>0.0002802934588235295</v>
       </c>
       <c r="I13" t="n">
         <v>1</v>
       </c>
       <c r="J13" t="n">
-        <v>0.0003430974112518748</v>
+        <v>0.0002802934588235295</v>
       </c>
       <c r="K13" t="n">
         <v>1</v>
@@ -939,7 +939,7 @@
         <v>49675</v>
       </c>
       <c r="B14" t="n">
-        <v>0.0003431676904081859</v>
+        <v>0.0002802934588235295</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -953,19 +953,19 @@
         <v>1</v>
       </c>
       <c r="F14" t="n">
-        <v>0.0003435431977095578</v>
+        <v>0.0002802934588235295</v>
       </c>
       <c r="G14" t="n">
         <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>0.0003436062498899332</v>
+        <v>0.0002802934588235295</v>
       </c>
       <c r="I14" t="n">
         <v>1</v>
       </c>
       <c r="J14" t="n">
-        <v>0.0003430974112518748</v>
+        <v>0.0002802934588235295</v>
       </c>
       <c r="K14" t="n">
         <v>1</v>
@@ -976,7 +976,7 @@
         <v>51502</v>
       </c>
       <c r="B15" t="n">
-        <v>0.0003431676904081859</v>
+        <v>0.0002802934588235295</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -990,19 +990,19 @@
         <v>1</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0003435431977095578</v>
+        <v>0.0002802934588235295</v>
       </c>
       <c r="G15" t="n">
         <v>1</v>
       </c>
       <c r="H15" t="n">
-        <v>0.0003436062498899331</v>
+        <v>0.0002802934588235295</v>
       </c>
       <c r="I15" t="n">
         <v>1</v>
       </c>
       <c r="J15" t="n">
-        <v>0.0003430974112518748</v>
+        <v>0.0002802934588235295</v>
       </c>
       <c r="K15" t="n">
         <v>1</v>
@@ -1013,7 +1013,7 @@
         <v>53328</v>
       </c>
       <c r="B16" t="n">
-        <v>0.0003431676904081859</v>
+        <v>0.0002802934588235295</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1027,19 +1027,19 @@
         <v>1</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0003435431977095578</v>
+        <v>0.0002802934588235295</v>
       </c>
       <c r="G16" t="n">
         <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>0.0003436062498899332</v>
+        <v>0.0002802934588235295</v>
       </c>
       <c r="I16" t="n">
         <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>0.0003430974112518748</v>
+        <v>0.0002802934588235295</v>
       </c>
       <c r="K16" t="n">
         <v>1</v>
@@ -1050,7 +1050,7 @@
         <v>46023</v>
       </c>
       <c r="B17" t="n">
-        <v>8.80628941302502e-05</v>
+        <v>0.008453392596820038</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -1064,19 +1064,19 @@
         <v>0.04548398400000001</v>
       </c>
       <c r="F17" t="n">
-        <v>4.816524335948026e-05</v>
+        <v>0.008453392596820037</v>
       </c>
       <c r="G17" t="n">
         <v>0.04548398400000001</v>
       </c>
       <c r="H17" t="n">
-        <v>4.146594919459856e-05</v>
+        <v>0.00845339259682003</v>
       </c>
       <c r="I17" t="n">
         <v>0.04548398400000001</v>
       </c>
       <c r="J17" t="n">
-        <v>9.553005448829466e-05</v>
+        <v>0.008607179538069604</v>
       </c>
       <c r="K17" t="n">
         <v>0.04548398400000001</v>
@@ -1087,7 +1087,7 @@
         <v>47849</v>
       </c>
       <c r="B18" t="n">
-        <v>8.80628941302502e-05</v>
+        <v>0.01044227126164197</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -1101,19 +1101,19 @@
         <v>0.04548398400000001</v>
       </c>
       <c r="F18" t="n">
-        <v>4.816524335948026e-05</v>
+        <v>0.01044227126164197</v>
       </c>
       <c r="G18" t="n">
         <v>0.04548398400000001</v>
       </c>
       <c r="H18" t="n">
-        <v>4.146594919459856e-05</v>
+        <v>0.01044227126164196</v>
       </c>
       <c r="I18" t="n">
         <v>0.04548398400000001</v>
       </c>
       <c r="J18" t="n">
-        <v>9.553005448829466e-05</v>
+        <v>0.0105707258474922</v>
       </c>
       <c r="K18" t="n">
         <v>0.04548398400000001</v>
@@ -1124,7 +1124,7 @@
         <v>49675</v>
       </c>
       <c r="B19" t="n">
-        <v>8.80628941302502e-05</v>
+        <v>0.01073413792594533</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -1138,19 +1138,19 @@
         <v>0.04548398400000001</v>
       </c>
       <c r="F19" t="n">
-        <v>4.816524335948026e-05</v>
+        <v>0.01062449000718652</v>
       </c>
       <c r="G19" t="n">
         <v>0.04548398400000001</v>
       </c>
       <c r="H19" t="n">
-        <v>4.146594919459856e-05</v>
+        <v>0.01062449000718651</v>
       </c>
       <c r="I19" t="n">
         <v>0.04548398400000001</v>
       </c>
       <c r="J19" t="n">
-        <v>9.553005448829466e-05</v>
+        <v>0.01084554704039429</v>
       </c>
       <c r="K19" t="n">
         <v>0.04548398400000001</v>
@@ -1161,7 +1161,7 @@
         <v>51502</v>
       </c>
       <c r="B20" t="n">
-        <v>8.806289413024723e-05</v>
+        <v>0.01079209734819434</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -1175,19 +1175,19 @@
         <v>0.04548398400000001</v>
       </c>
       <c r="F20" t="n">
-        <v>4.816524335948726e-05</v>
+        <v>0.01083372070825135</v>
       </c>
       <c r="G20" t="n">
         <v>0.04548398400000001</v>
       </c>
       <c r="H20" t="n">
-        <v>4.146594919460433e-05</v>
+        <v>0.009088581261641972</v>
       </c>
       <c r="I20" t="n">
         <v>0.04548398400000001</v>
       </c>
       <c r="J20" t="n">
-        <v>9.55300544882991e-05</v>
+        <v>0.0092170358474922</v>
       </c>
       <c r="K20" t="n">
         <v>0.04548398400000001</v>
@@ -1198,7 +1198,7 @@
         <v>53328</v>
       </c>
       <c r="B21" t="n">
-        <v>8.806289413024723e-05</v>
+        <v>0.009346294185394939</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -1212,19 +1212,19 @@
         <v>0.04548398400000001</v>
       </c>
       <c r="F21" t="n">
-        <v>4.816524335948726e-05</v>
+        <v>0.009380447925945338</v>
       </c>
       <c r="G21" t="n">
         <v>0.04548398400000001</v>
       </c>
       <c r="H21" t="n">
-        <v>4.146594919460432e-05</v>
+        <v>0.009438407348194323</v>
       </c>
       <c r="I21" t="n">
         <v>0.04548398400000001</v>
       </c>
       <c r="J21" t="n">
-        <v>9.55300544882991e-05</v>
+        <v>0.008109711307756401</v>
       </c>
       <c r="K21" t="n">
         <v>0.04548398400000001</v>
@@ -1551,13 +1551,13 @@
         <v>0.04548398400000001</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>0.00135368999999999</v>
       </c>
       <c r="I30" t="n">
         <v>0.04548398400000001</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>0.00135369</v>
       </c>
       <c r="K30" t="n">
         <v>0.04548398400000001</v>
@@ -1568,7 +1568,7 @@
         <v>53328</v>
       </c>
       <c r="B31" t="n">
-        <v>0</v>
+        <v>0.00135369</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -1582,19 +1582,19 @@
         <v>0.04548398400000001</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>0.00135368999999999</v>
       </c>
       <c r="G31" t="n">
         <v>0.04548398400000001</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>0.00135369</v>
       </c>
       <c r="I31" t="n">
         <v>0.04548398400000001</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>0.002461014539735807</v>
       </c>
       <c r="K31" t="n">
         <v>0.04548398400000001</v>
@@ -2160,7 +2160,7 @@
         <v>46023</v>
       </c>
       <c r="B47" t="n">
-        <v>0.04173393865152786</v>
+        <v>0.03812215132117999</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -2174,19 +2174,19 @@
         <v>0.3728231852869826</v>
       </c>
       <c r="F47" t="n">
-        <v>0.04658574721973147</v>
+        <v>0.0389877397383804</v>
       </c>
       <c r="G47" t="n">
         <v>0.3728231852869826</v>
       </c>
       <c r="H47" t="n">
-        <v>0.04674545582998477</v>
+        <v>0.03880842878542077</v>
       </c>
       <c r="I47" t="n">
         <v>0.3728231852869826</v>
       </c>
       <c r="J47" t="n">
-        <v>0.04186854527531282</v>
+        <v>0.03787904166504838</v>
       </c>
       <c r="K47" t="n">
         <v>0.3728231852869826</v>
@@ -2197,7 +2197,7 @@
         <v>47849</v>
       </c>
       <c r="B48" t="n">
-        <v>0.04173393865152786</v>
+        <v>0.03812215132117999</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -2211,19 +2211,19 @@
         <v>0.3728231852869826</v>
       </c>
       <c r="F48" t="n">
-        <v>0.04658574721973147</v>
+        <v>0.0389877397383804</v>
       </c>
       <c r="G48" t="n">
         <v>0.3728231852869826</v>
       </c>
       <c r="H48" t="n">
-        <v>0.04674545582998477</v>
+        <v>0.03880842878542077</v>
       </c>
       <c r="I48" t="n">
         <v>0.3728231852869826</v>
       </c>
       <c r="J48" t="n">
-        <v>0.04186854527531282</v>
+        <v>0.03787904166504838</v>
       </c>
       <c r="K48" t="n">
         <v>0.3728231852869826</v>
@@ -2234,7 +2234,7 @@
         <v>49675</v>
       </c>
       <c r="B49" t="n">
-        <v>0.04173393865152786</v>
+        <v>0.03812215132117999</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -2248,19 +2248,19 @@
         <v>0.3728231852869826</v>
       </c>
       <c r="F49" t="n">
-        <v>0.04658574721973147</v>
+        <v>0.0389877397383804</v>
       </c>
       <c r="G49" t="n">
         <v>0.3728231852869826</v>
       </c>
       <c r="H49" t="n">
-        <v>0.04674545582998477</v>
+        <v>0.03880842878542077</v>
       </c>
       <c r="I49" t="n">
         <v>0.3728231852869826</v>
       </c>
       <c r="J49" t="n">
-        <v>0.04186854527531282</v>
+        <v>0.03787904166504838</v>
       </c>
       <c r="K49" t="n">
         <v>0.3728231852869826</v>
@@ -2345,7 +2345,7 @@
         <v>46023</v>
       </c>
       <c r="B52" t="n">
-        <v>0.1149903050712238</v>
+        <v>0.1171078115609403</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -2359,19 +2359,19 @@
         <v>0.3728231852869826</v>
       </c>
       <c r="F52" t="n">
-        <v>0.1019153100991283</v>
+        <v>0.1056925256689784</v>
       </c>
       <c r="G52" t="n">
         <v>0.3728231852869826</v>
       </c>
       <c r="H52" t="n">
-        <v>0.1165824094053396</v>
+        <v>0.105311999415009</v>
       </c>
       <c r="I52" t="n">
         <v>0.1004499548106655</v>
       </c>
       <c r="J52" t="n">
-        <v>0.1211782910848568</v>
+        <v>0.1167782772208998</v>
       </c>
       <c r="K52" t="n">
         <v>0.1004499548106655</v>
@@ -2382,7 +2382,7 @@
         <v>47849</v>
       </c>
       <c r="B53" t="n">
-        <v>0.1149903050712238</v>
+        <v>0.1171078115609403</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -2396,19 +2396,19 @@
         <v>0.3728231852869826</v>
       </c>
       <c r="F53" t="n">
-        <v>0.1019153100991283</v>
+        <v>0.1056925256689784</v>
       </c>
       <c r="G53" t="n">
         <v>0.3728231852869826</v>
       </c>
       <c r="H53" t="n">
-        <v>0.1165824094053396</v>
+        <v>0.105311999415009</v>
       </c>
       <c r="I53" t="n">
         <v>0.1481906999845719</v>
       </c>
       <c r="J53" t="n">
-        <v>0.1211782910848568</v>
+        <v>0.1167782772208998</v>
       </c>
       <c r="K53" t="n">
         <v>0.1481906999845719</v>
@@ -2419,7 +2419,7 @@
         <v>49675</v>
       </c>
       <c r="B54" t="n">
-        <v>0.1149903050712238</v>
+        <v>0.1171078115609403</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -2433,19 +2433,19 @@
         <v>0.3728231852869826</v>
       </c>
       <c r="F54" t="n">
-        <v>0.1019153100991283</v>
+        <v>0.1056925256689784</v>
       </c>
       <c r="G54" t="n">
         <v>0.3728231852869826</v>
       </c>
       <c r="H54" t="n">
-        <v>0.1165824094053396</v>
+        <v>0.105311999415009</v>
       </c>
       <c r="I54" t="n">
         <v>0.1755625367288213</v>
       </c>
       <c r="J54" t="n">
-        <v>0.1211782910848568</v>
+        <v>0.1167782772208998</v>
       </c>
       <c r="K54" t="n">
         <v>0.1755625367288213</v>
@@ -2456,7 +2456,7 @@
         <v>51502</v>
       </c>
       <c r="B55" t="n">
-        <v>0.1301083925070466</v>
+        <v>0.1263911782487409</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -2470,19 +2470,19 @@
         <v>0.3728231852869826</v>
       </c>
       <c r="F55" t="n">
-        <v>0.1278082040312937</v>
+        <v>0.1261473877599102</v>
       </c>
       <c r="G55" t="n">
         <v>0.3728231852869826</v>
       </c>
       <c r="H55" t="n">
-        <v>0.1278056753319267</v>
+        <v>0.1261473877599101</v>
       </c>
       <c r="I55" t="n">
         <v>0.1931737428836243</v>
       </c>
       <c r="J55" t="n">
-        <v>0.1301088429109509</v>
+        <v>0.1264850892131472</v>
       </c>
       <c r="K55" t="n">
         <v>0.1931737428836243</v>
@@ -2493,7 +2493,7 @@
         <v>53328</v>
       </c>
       <c r="B56" t="n">
-        <v>0.1301083925070466</v>
+        <v>0.1263911782487409</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -2507,19 +2507,19 @@
         <v>0.3728231852869826</v>
       </c>
       <c r="F56" t="n">
-        <v>0.1278082040312937</v>
+        <v>0.1261473877599102</v>
       </c>
       <c r="G56" t="n">
         <v>0.3728231852869826</v>
       </c>
       <c r="H56" t="n">
-        <v>0.1278056753319267</v>
+        <v>0.1261473877599101</v>
       </c>
       <c r="I56" t="n">
         <v>0.2054159783640118</v>
       </c>
       <c r="J56" t="n">
-        <v>0.1301088429109509</v>
+        <v>0.1264850892131472</v>
       </c>
       <c r="K56" t="n">
         <v>0.2054159783640118</v>
@@ -2715,7 +2715,7 @@
         <v>46023</v>
       </c>
       <c r="B62" t="n">
-        <v>0.04413696162664221</v>
+        <v>0.00522398793024938</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -2729,19 +2729,19 @@
         <v>0.3728231852869826</v>
       </c>
       <c r="F62" t="n">
-        <v>0.04555155061631985</v>
+        <v>0.005223987930249386</v>
       </c>
       <c r="G62" t="n">
         <v>0.3728231852869826</v>
       </c>
       <c r="H62" t="n">
-        <v>0.04573144611930596</v>
+        <v>0.005223987930249412</v>
       </c>
       <c r="I62" t="n">
         <v>0.3728231852869826</v>
       </c>
       <c r="J62" t="n">
-        <v>0.04604301480033433</v>
+        <v>0.005524351036817763</v>
       </c>
       <c r="K62" t="n">
         <v>0.3728231852869826</v>
@@ -2752,7 +2752,7 @@
         <v>47849</v>
       </c>
       <c r="B63" t="n">
-        <v>0.04413696162664221</v>
+        <v>0.00522398793024938</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -2766,19 +2766,19 @@
         <v>0.3728231852869826</v>
       </c>
       <c r="F63" t="n">
-        <v>0.04555155061631985</v>
+        <v>0.005223987930249386</v>
       </c>
       <c r="G63" t="n">
         <v>0.3728231852869826</v>
       </c>
       <c r="H63" t="n">
-        <v>0.04573144611930596</v>
+        <v>0.005223987930249412</v>
       </c>
       <c r="I63" t="n">
         <v>0.3728231852869826</v>
       </c>
       <c r="J63" t="n">
-        <v>0.04604301480033433</v>
+        <v>0.005524351036817763</v>
       </c>
       <c r="K63" t="n">
         <v>0.3728231852869826</v>
@@ -2789,7 +2789,7 @@
         <v>49675</v>
       </c>
       <c r="B64" t="n">
-        <v>0.04413696162664221</v>
+        <v>0.00522398793024938</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -2803,19 +2803,19 @@
         <v>0.3728231852869826</v>
       </c>
       <c r="F64" t="n">
-        <v>0.04555155061631985</v>
+        <v>0.005223987930249386</v>
       </c>
       <c r="G64" t="n">
         <v>0.3728231852869826</v>
       </c>
       <c r="H64" t="n">
-        <v>0.04573144611930596</v>
+        <v>0.005223987930249412</v>
       </c>
       <c r="I64" t="n">
         <v>0.3728231852869826</v>
       </c>
       <c r="J64" t="n">
-        <v>0.04604301480033433</v>
+        <v>0.005524351036817763</v>
       </c>
       <c r="K64" t="n">
         <v>0.3728231852869826</v>
@@ -2826,7 +2826,7 @@
         <v>51502</v>
       </c>
       <c r="B65" t="n">
-        <v>0.05248153822093977</v>
+        <v>0.02015492614088564</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -2840,19 +2840,19 @@
         <v>0.3728231852869826</v>
       </c>
       <c r="F65" t="n">
-        <v>0.05476686884180583</v>
+        <v>0.02040153445201794</v>
       </c>
       <c r="G65" t="n">
         <v>0.3728231852869826</v>
       </c>
       <c r="H65" t="n">
-        <v>0.05476174690073309</v>
+        <v>0.02037503406908123</v>
       </c>
       <c r="I65" t="n">
         <v>0.3728231852869826</v>
       </c>
       <c r="J65" t="n">
-        <v>0.05248108781703551</v>
+        <v>0.02014565765343312</v>
       </c>
       <c r="K65" t="n">
         <v>0.3728231852869826</v>
@@ -2863,7 +2863,7 @@
         <v>53328</v>
       </c>
       <c r="B66" t="n">
-        <v>0.07499021469401072</v>
+        <v>0.03345698758191588</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -2877,19 +2877,19 @@
         <v>0.3728231852869826</v>
       </c>
       <c r="F66" t="n">
-        <v>0.07727554531487678</v>
+        <v>0.03370383141613122</v>
       </c>
       <c r="G66" t="n">
         <v>0.3728231852869826</v>
       </c>
       <c r="H66" t="n">
-        <v>0.07727042337380405</v>
+        <v>0.03370901299014237</v>
       </c>
       <c r="I66" t="n">
         <v>0.3728231852869826</v>
       </c>
       <c r="J66" t="n">
-        <v>0.07498976429010647</v>
+        <v>0.03345854575864842</v>
       </c>
       <c r="K66" t="n">
         <v>0.3728231852869826</v>
@@ -3108,13 +3108,13 @@
         <v>0</v>
       </c>
       <c r="I72" t="n">
-        <v>0.0113171511381666</v>
+        <v>0.3728231852869826</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>0.0113171511381666</v>
+        <v>0.3728231852869826</v>
       </c>
     </row>
     <row r="73">
@@ -3145,13 +3145,13 @@
         <v>0</v>
       </c>
       <c r="I73" t="n">
-        <v>0.01916694792094811</v>
+        <v>0.3728231852869826</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>0.01916694792094811</v>
+        <v>0.3728231852869826</v>
       </c>
     </row>
     <row r="74">
@@ -3182,13 +3182,13 @@
         <v>0</v>
       </c>
       <c r="I74" t="n">
-        <v>0.02523290795316862</v>
+        <v>0.3728231852869826</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>0.02523290795316862</v>
+        <v>0.3728231852869826</v>
       </c>
     </row>
     <row r="75">
@@ -3219,13 +3219,13 @@
         <v>0</v>
       </c>
       <c r="I75" t="n">
-        <v>0.0301645426812714</v>
+        <v>0.3728231852869826</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>0.0301645426812714</v>
+        <v>0.3728231852869826</v>
       </c>
     </row>
     <row r="76">
@@ -3256,13 +3256,13 @@
         <v>0</v>
       </c>
       <c r="I76" t="n">
-        <v>0.0343039870084621</v>
+        <v>0.3728231852869826</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
       </c>
       <c r="K76" t="n">
-        <v>0.0343039870084621</v>
+        <v>0.3728231852869826</v>
       </c>
     </row>
     <row r="77">
@@ -3270,7 +3270,7 @@
         <v>46023</v>
       </c>
       <c r="B77" t="n">
-        <v>0.02347765731673471</v>
+        <v>0.01440232238297027</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -3284,22 +3284,22 @@
         <v>0.3728231852869826</v>
       </c>
       <c r="F77" t="n">
-        <v>0.03025667476714378</v>
+        <v>0.02495201985773176</v>
       </c>
       <c r="G77" t="n">
         <v>0.3728231852869826</v>
       </c>
       <c r="H77" t="n">
-        <v>0.01524204952955736</v>
+        <v>0.0255118570646608</v>
       </c>
       <c r="I77" t="n">
-        <v>0.0113171511381666</v>
+        <v>0.3728231852869826</v>
       </c>
       <c r="J77" t="n">
-        <v>0.01524204952955736</v>
+        <v>0.01506015243321412</v>
       </c>
       <c r="K77" t="n">
-        <v>0.0113171511381666</v>
+        <v>0.3728231852869826</v>
       </c>
     </row>
     <row r="78">
@@ -3307,7 +3307,7 @@
         <v>47849</v>
       </c>
       <c r="B78" t="n">
-        <v>0.02347765731673471</v>
+        <v>0.01440232238297027</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -3321,22 +3321,22 @@
         <v>0.3728231852869826</v>
       </c>
       <c r="F78" t="n">
-        <v>0.03025667476714378</v>
+        <v>0.02495201985773176</v>
       </c>
       <c r="G78" t="n">
         <v>0.3728231852869826</v>
       </c>
       <c r="H78" t="n">
-        <v>0.01524204952955736</v>
+        <v>0.0255118570646608</v>
       </c>
       <c r="I78" t="n">
-        <v>0.01916694792094811</v>
+        <v>0.3728231852869826</v>
       </c>
       <c r="J78" t="n">
-        <v>0.01524204952955736</v>
+        <v>0.01506015243321412</v>
       </c>
       <c r="K78" t="n">
-        <v>0.01916694792094811</v>
+        <v>0.3728231852869826</v>
       </c>
     </row>
     <row r="79">
@@ -3344,7 +3344,7 @@
         <v>49675</v>
       </c>
       <c r="B79" t="n">
-        <v>0.02347765731673471</v>
+        <v>0.01440232238297027</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -3358,22 +3358,22 @@
         <v>0.3728231852869826</v>
       </c>
       <c r="F79" t="n">
-        <v>0.03025667476714378</v>
+        <v>0.02495201985773176</v>
       </c>
       <c r="G79" t="n">
         <v>0.3728231852869826</v>
       </c>
       <c r="H79" t="n">
-        <v>0.01524204952955736</v>
+        <v>0.0255118570646608</v>
       </c>
       <c r="I79" t="n">
-        <v>0.02523290795316862</v>
+        <v>0.3728231852869826</v>
       </c>
       <c r="J79" t="n">
-        <v>0.01524204952955736</v>
+        <v>0.01506015243321412</v>
       </c>
       <c r="K79" t="n">
-        <v>0.02523290795316862</v>
+        <v>0.3728231852869826</v>
       </c>
     </row>
     <row r="80">
@@ -3404,13 +3404,13 @@
         <v>0</v>
       </c>
       <c r="I80" t="n">
-        <v>0.0301645426812714</v>
+        <v>0.3728231852869826</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
       </c>
       <c r="K80" t="n">
-        <v>0.0301645426812714</v>
+        <v>0.3728231852869826</v>
       </c>
     </row>
     <row r="81">
@@ -3441,13 +3441,13 @@
         <v>0</v>
       </c>
       <c r="I81" t="n">
-        <v>0.0343039870084621</v>
+        <v>0.3728231852869826</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
       </c>
       <c r="K81" t="n">
-        <v>0.0343039870084621</v>
+        <v>0.3728231852869826</v>
       </c>
     </row>
     <row r="82">
